--- a/cocos/GC_L0~L2_有效学习目标.xlsx
+++ b/cocos/GC_L0~L2_有效学习目标.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="495" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="405" uniqueCount="39">
   <si>
     <t>课型</t>
   </si>
@@ -68,9 +68,6 @@
   </si>
   <si>
     <t>sentence_pattern_structure</t>
-  </si>
-  <si>
-    <t>INTERACTION-SPEAK</t>
   </si>
   <si>
     <t>Level1</t>
@@ -140,6 +137,9 @@
   </si>
   <si>
     <t>functional_language</t>
+  </si>
+  <si>
+    <t>INTERACTION-SPEAK</t>
   </si>
   <si>
     <t>嘉年华</t>
@@ -769,7 +769,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -799,9 +799,6 @@
           <etc:displayText val="2"/>
         </ext>
       </extLst>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -1114,7 +1111,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:AO207"/>
+  <dimension ref="A1:AO189"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="17.5309734513274" customWidth="1"/>
@@ -1402,7 +1399,7 @@
         <v>12</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="F6" s="2"/>
       <c r="G6" s="2"/>
@@ -1449,13 +1446,13 @@
         <v>6</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F7" s="2"/>
       <c r="G7" s="2"/>
@@ -1502,13 +1499,13 @@
         <v>6</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="F8" s="2"/>
       <c r="G8" s="2"/>
@@ -1555,13 +1552,13 @@
         <v>6</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D9" s="2" t="s">
         <v>8</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="F9" s="2"/>
       <c r="G9" s="2"/>
@@ -1608,13 +1605,13 @@
         <v>6</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D10" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="F10" s="2"/>
       <c r="G10" s="2"/>
@@ -1661,10 +1658,10 @@
         <v>6</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>11</v>
@@ -1717,10 +1714,10 @@
         <v>14</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F12" s="2"/>
       <c r="G12" s="2"/>
@@ -1770,7 +1767,7 @@
         <v>14</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>9</v>
@@ -1823,10 +1820,10 @@
         <v>14</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="F14" s="2"/>
       <c r="G14" s="2"/>
@@ -1876,10 +1873,10 @@
         <v>14</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="F15" s="2"/>
       <c r="G15" s="2"/>
@@ -1926,13 +1923,13 @@
         <v>6</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D16" s="2" t="s">
         <v>8</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="F16" s="2"/>
       <c r="G16" s="2"/>
@@ -1979,13 +1976,13 @@
         <v>6</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D17" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="F17" s="2"/>
       <c r="G17" s="2"/>
@@ -2032,13 +2029,13 @@
         <v>6</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="F18" s="2"/>
       <c r="G18" s="2"/>
@@ -2085,10 +2082,10 @@
         <v>6</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E19" s="2" t="s">
         <v>16</v>
@@ -2132,19 +2129,19 @@
     </row>
     <row r="20" spans="1:41">
       <c r="A20" s="2" t="s">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="F20" s="2"/>
       <c r="G20" s="2"/>
@@ -2185,19 +2182,19 @@
     </row>
     <row r="21" spans="1:41">
       <c r="A21" s="2" t="s">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="F21" s="2"/>
       <c r="G21" s="2"/>
@@ -2238,19 +2235,19 @@
     </row>
     <row r="22" spans="1:41">
       <c r="A22" s="2" t="s">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="F22" s="2"/>
       <c r="G22" s="2"/>
@@ -2291,19 +2288,19 @@
     </row>
     <row r="23" spans="1:41">
       <c r="A23" s="2" t="s">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F23" s="2"/>
       <c r="G23" s="2"/>
@@ -2344,19 +2341,19 @@
     </row>
     <row r="24" spans="1:41">
       <c r="A24" s="2" t="s">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="F24" s="2"/>
       <c r="G24" s="2"/>
@@ -2397,19 +2394,19 @@
     </row>
     <row r="25" spans="1:41">
       <c r="A25" s="2" t="s">
-        <v>5</v>
+        <v>24</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>6</v>
+        <v>25</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>12</v>
+        <v>26</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="F25" s="2"/>
       <c r="G25" s="2"/>
@@ -2450,19 +2447,19 @@
     </row>
     <row r="26" spans="1:41">
       <c r="A26" s="2" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="F26" s="2"/>
       <c r="G26" s="2"/>
@@ -2503,19 +2500,19 @@
     </row>
     <row r="27" spans="1:41">
       <c r="A27" s="2" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="F27" s="2"/>
       <c r="G27" s="2"/>
@@ -2556,19 +2553,19 @@
     </row>
     <row r="28" spans="1:41">
       <c r="A28" s="2" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>23</v>
+        <v>9</v>
       </c>
       <c r="F28" s="2"/>
       <c r="G28" s="2"/>
@@ -2609,19 +2606,19 @@
     </row>
     <row r="29" spans="1:41">
       <c r="A29" s="2" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="F29" s="2"/>
       <c r="G29" s="2"/>
@@ -2662,19 +2659,19 @@
     </row>
     <row r="30" spans="1:41">
       <c r="A30" s="2" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>11</v>
+        <v>28</v>
       </c>
       <c r="F30" s="2"/>
       <c r="G30" s="2"/>
@@ -2715,10 +2712,10 @@
     </row>
     <row r="31" spans="1:41">
       <c r="A31" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B31" s="2" t="s">
         <v>25</v>
-      </c>
-      <c r="B31" s="2" t="s">
-        <v>26</v>
       </c>
       <c r="C31" s="2" t="s">
         <v>14</v>
@@ -2727,7 +2724,7 @@
         <v>27</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="F31" s="2"/>
       <c r="G31" s="2"/>
@@ -2768,19 +2765,19 @@
     </row>
     <row r="32" spans="1:41">
       <c r="A32" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B32" s="2" t="s">
         <v>25</v>
-      </c>
-      <c r="B32" s="2" t="s">
-        <v>26</v>
       </c>
       <c r="C32" s="2" t="s">
         <v>14</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>29</v>
+        <v>9</v>
       </c>
       <c r="F32" s="2"/>
       <c r="G32" s="2"/>
@@ -2821,19 +2818,19 @@
     </row>
     <row r="33" spans="1:41">
       <c r="A33" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="B33" s="2" t="s">
-        <v>26</v>
+        <v>30</v>
+      </c>
+      <c r="B33" s="3" t="s">
+        <v>31</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>28</v>
+        <v>12</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>30</v>
+        <v>11</v>
       </c>
       <c r="F33" s="2"/>
       <c r="G33" s="2"/>
@@ -2874,19 +2871,19 @@
     </row>
     <row r="34" spans="1:41">
       <c r="A34" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="B34" s="2" t="s">
-        <v>26</v>
+        <v>30</v>
+      </c>
+      <c r="B34" s="3" t="s">
+        <v>31</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="F34" s="2"/>
       <c r="G34" s="2"/>
@@ -2927,19 +2924,19 @@
     </row>
     <row r="35" spans="1:41">
       <c r="A35" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="B35" s="2" t="s">
-        <v>26</v>
+        <v>30</v>
+      </c>
+      <c r="B35" s="3" t="s">
+        <v>31</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="F35" s="2"/>
       <c r="G35" s="2"/>
@@ -2980,19 +2977,19 @@
     </row>
     <row r="36" spans="1:41">
       <c r="A36" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="B36" s="2" t="s">
-        <v>26</v>
+        <v>30</v>
+      </c>
+      <c r="B36" s="3" t="s">
+        <v>31</v>
       </c>
       <c r="C36" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D36" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="E36" s="2" t="s">
         <v>15</v>
-      </c>
-      <c r="D36" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="E36" s="2" t="s">
-        <v>29</v>
       </c>
       <c r="F36" s="2"/>
       <c r="G36" s="2"/>
@@ -3033,19 +3030,19 @@
     </row>
     <row r="37" spans="1:41">
       <c r="A37" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="B37" s="2" t="s">
-        <v>26</v>
+        <v>30</v>
+      </c>
+      <c r="B37" s="3" t="s">
+        <v>31</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>28</v>
+        <v>12</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>30</v>
+        <v>11</v>
       </c>
       <c r="F37" s="2"/>
       <c r="G37" s="2"/>
@@ -3086,19 +3083,19 @@
     </row>
     <row r="38" spans="1:41">
       <c r="A38" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="B38" s="2" t="s">
-        <v>26</v>
+        <v>30</v>
+      </c>
+      <c r="B38" s="3" t="s">
+        <v>31</v>
       </c>
       <c r="C38" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D38" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="E38" s="2" t="s">
         <v>15</v>
-      </c>
-      <c r="D38" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="E38" s="2" t="s">
-        <v>9</v>
       </c>
       <c r="F38" s="2"/>
       <c r="G38" s="2"/>
@@ -3139,19 +3136,19 @@
     </row>
     <row r="39" spans="1:41">
       <c r="A39" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="B39" s="3" t="s">
-        <v>32</v>
+        <v>33</v>
+      </c>
+      <c r="B39" s="2" t="s">
+        <v>34</v>
       </c>
       <c r="C39" s="2" t="s">
         <v>7</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="F39" s="2"/>
       <c r="G39" s="2"/>
@@ -3192,16 +3189,16 @@
     </row>
     <row r="40" spans="1:41">
       <c r="A40" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="B40" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="C40" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="B40" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="C40" s="4" t="s">
         <v>7</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E40" s="2" t="s">
         <v>11</v>
@@ -3245,19 +3242,19 @@
     </row>
     <row r="41" spans="1:41">
       <c r="A41" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="B41" s="3" t="s">
-        <v>32</v>
+        <v>33</v>
+      </c>
+      <c r="B41" s="2" t="s">
+        <v>34</v>
       </c>
       <c r="C41" s="2" t="s">
         <v>7</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>33</v>
+        <v>12</v>
       </c>
       <c r="E41" s="2" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="F41" s="2"/>
       <c r="G41" s="2"/>
@@ -3298,19 +3295,19 @@
     </row>
     <row r="42" spans="1:41">
       <c r="A42" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="B42" s="3" t="s">
-        <v>32</v>
+        <v>33</v>
+      </c>
+      <c r="B42" s="2" t="s">
+        <v>34</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>12</v>
+        <v>35</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>9</v>
+        <v>36</v>
       </c>
       <c r="F42" s="2"/>
       <c r="G42" s="2"/>
@@ -3351,16 +3348,16 @@
     </row>
     <row r="43" spans="1:41">
       <c r="A43" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="B43" s="3" t="s">
-        <v>32</v>
+        <v>33</v>
+      </c>
+      <c r="B43" s="2" t="s">
+        <v>34</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="E43" s="2" t="s">
         <v>11</v>
@@ -3404,19 +3401,19 @@
     </row>
     <row r="44" spans="1:41">
       <c r="A44" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="B44" s="3" t="s">
-        <v>32</v>
+        <v>33</v>
+      </c>
+      <c r="B44" s="2" t="s">
+        <v>34</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>33</v>
+        <v>10</v>
       </c>
       <c r="E44" s="2" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="F44" s="2"/>
       <c r="G44" s="2"/>
@@ -3457,19 +3454,19 @@
     </row>
     <row r="45" spans="1:41">
       <c r="A45" s="2" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="D45" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E45" s="2" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="F45" s="2"/>
       <c r="G45" s="2"/>
@@ -3510,19 +3507,19 @@
     </row>
     <row r="46" spans="1:41">
       <c r="A46" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="B46" s="3" t="s">
-        <v>32</v>
+        <v>33</v>
+      </c>
+      <c r="B46" s="2" t="s">
+        <v>34</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>12</v>
+        <v>35</v>
       </c>
       <c r="E46" s="2" t="s">
-        <v>11</v>
+        <v>36</v>
       </c>
       <c r="F46" s="2"/>
       <c r="G46" s="2"/>
@@ -3563,19 +3560,19 @@
     </row>
     <row r="47" spans="1:41">
       <c r="A47" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="B47" s="3" t="s">
-        <v>32</v>
+        <v>33</v>
+      </c>
+      <c r="B47" s="2" t="s">
+        <v>34</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>33</v>
+        <v>8</v>
       </c>
       <c r="E47" s="2" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="F47" s="2"/>
       <c r="G47" s="2"/>
@@ -3616,16 +3613,16 @@
     </row>
     <row r="48" spans="1:41">
       <c r="A48" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="B48" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="B48" s="2" t="s">
-        <v>35</v>
-      </c>
       <c r="C48" s="2" t="s">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E48" s="2" t="s">
         <v>11</v>
@@ -3669,16 +3666,16 @@
     </row>
     <row r="49" spans="1:41">
       <c r="A49" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="B49" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="B49" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="C49" s="4" t="s">
-        <v>7</v>
+      <c r="C49" s="2" t="s">
+        <v>14</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E49" s="2" t="s">
         <v>11</v>
@@ -3722,19 +3719,19 @@
     </row>
     <row r="50" spans="1:41">
       <c r="A50" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="B50" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="B50" s="2" t="s">
+      <c r="C50" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D50" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="C50" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D50" s="2" t="s">
-        <v>12</v>
-      </c>
       <c r="E50" s="2" t="s">
-        <v>11</v>
+        <v>36</v>
       </c>
       <c r="F50" s="2"/>
       <c r="G50" s="2"/>
@@ -3775,19 +3772,19 @@
     </row>
     <row r="51" spans="1:41">
       <c r="A51" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="B51" s="2" t="s">
-        <v>35</v>
+        <v>37</v>
+      </c>
+      <c r="B51" s="3" t="s">
+        <v>38</v>
       </c>
       <c r="C51" s="2" t="s">
         <v>7</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="E51" s="2" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="F51" s="2"/>
       <c r="G51" s="2"/>
@@ -3828,19 +3825,19 @@
     </row>
     <row r="52" spans="1:41">
       <c r="A52" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="B52" s="2" t="s">
-        <v>35</v>
+        <v>37</v>
+      </c>
+      <c r="B52" s="3" t="s">
+        <v>38</v>
       </c>
       <c r="C52" s="2" t="s">
         <v>7</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>36</v>
+        <v>10</v>
       </c>
       <c r="E52" s="2" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="F52" s="2"/>
       <c r="G52" s="2"/>
@@ -3881,13 +3878,13 @@
     </row>
     <row r="53" spans="1:41">
       <c r="A53" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="B53" s="2" t="s">
-        <v>35</v>
+        <v>37</v>
+      </c>
+      <c r="B53" s="3" t="s">
+        <v>38</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="D53" s="2" t="s">
         <v>8</v>
@@ -3934,13 +3931,13 @@
     </row>
     <row r="54" spans="1:41">
       <c r="A54" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="B54" s="2" t="s">
-        <v>35</v>
+        <v>37</v>
+      </c>
+      <c r="B54" s="3" t="s">
+        <v>38</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="D54" s="2" t="s">
         <v>10</v>
@@ -3987,13 +3984,13 @@
     </row>
     <row r="55" spans="1:41">
       <c r="A55" s="2" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="D55" s="2" t="s">
         <v>12</v>
@@ -4040,19 +4037,19 @@
     </row>
     <row r="56" spans="1:41">
       <c r="A56" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="B56" s="2" t="s">
-        <v>35</v>
+        <v>37</v>
+      </c>
+      <c r="B56" s="3" t="s">
+        <v>38</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="D56" s="2" t="s">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="E56" s="2" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="F56" s="2"/>
       <c r="G56" s="2"/>
@@ -4093,19 +4090,19 @@
     </row>
     <row r="57" spans="1:41">
       <c r="A57" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="B57" s="2" t="s">
-        <v>35</v>
+        <v>37</v>
+      </c>
+      <c r="B57" s="3" t="s">
+        <v>38</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="D57" s="2" t="s">
-        <v>36</v>
+        <v>19</v>
       </c>
       <c r="E57" s="2" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="F57" s="2"/>
       <c r="G57" s="2"/>
@@ -4146,19 +4143,19 @@
     </row>
     <row r="58" spans="1:41">
       <c r="A58" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="B58" s="2" t="s">
-        <v>35</v>
+        <v>37</v>
+      </c>
+      <c r="B58" s="3" t="s">
+        <v>38</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="D58" s="2" t="s">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="E58" s="2" t="s">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="F58" s="2"/>
       <c r="G58" s="2"/>
@@ -4199,19 +4196,19 @@
     </row>
     <row r="59" spans="1:41">
       <c r="A59" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="B59" s="2" t="s">
-        <v>35</v>
+        <v>37</v>
+      </c>
+      <c r="B59" s="3" t="s">
+        <v>38</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="D59" s="2" t="s">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="E59" s="2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F59" s="2"/>
       <c r="G59" s="2"/>
@@ -4252,16 +4249,16 @@
     </row>
     <row r="60" spans="1:41">
       <c r="A60" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="B60" s="2" t="s">
-        <v>35</v>
+        <v>37</v>
+      </c>
+      <c r="B60" s="3" t="s">
+        <v>38</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="D60" s="2" t="s">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="E60" s="2" t="s">
         <v>11</v>
@@ -4305,19 +4302,19 @@
     </row>
     <row r="61" spans="1:41">
       <c r="A61" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="B61" s="2" t="s">
-        <v>35</v>
+        <v>37</v>
+      </c>
+      <c r="B61" s="3" t="s">
+        <v>38</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="D61" s="2" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="E61" s="2" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="F61" s="2"/>
       <c r="G61" s="2"/>
@@ -4358,19 +4355,19 @@
     </row>
     <row r="62" spans="1:41">
       <c r="A62" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="B62" s="2" t="s">
-        <v>35</v>
+        <v>37</v>
+      </c>
+      <c r="B62" s="3" t="s">
+        <v>38</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="D62" s="2" t="s">
-        <v>36</v>
+        <v>10</v>
       </c>
       <c r="E62" s="2" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="F62" s="2"/>
       <c r="G62" s="2"/>
@@ -4413,17 +4410,17 @@
       <c r="A63" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="B63" s="5" t="s">
+      <c r="B63" s="3" t="s">
         <v>38</v>
       </c>
       <c r="C63" s="2" t="s">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="D63" s="2" t="s">
         <v>8</v>
       </c>
       <c r="E63" s="2" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="F63" s="2"/>
       <c r="G63" s="2"/>
@@ -4466,17 +4463,17 @@
       <c r="A64" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="B64" s="5" t="s">
+      <c r="B64" s="3" t="s">
         <v>38</v>
       </c>
       <c r="C64" s="2" t="s">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="D64" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E64" s="2" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="F64" s="2"/>
       <c r="G64" s="2"/>
@@ -4519,14 +4516,14 @@
       <c r="A65" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="B65" s="5" t="s">
+      <c r="B65" s="3" t="s">
         <v>38</v>
       </c>
       <c r="C65" s="2" t="s">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="D65" s="2" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="E65" s="2" t="s">
         <v>11</v>
@@ -4572,17 +4569,17 @@
       <c r="A66" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="B66" s="5" t="s">
+      <c r="B66" s="3" t="s">
         <v>38</v>
       </c>
       <c r="C66" s="2" t="s">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="D66" s="2" t="s">
-        <v>10</v>
+        <v>26</v>
       </c>
       <c r="E66" s="2" t="s">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="F66" s="2"/>
       <c r="G66" s="2"/>
@@ -4625,17 +4622,17 @@
       <c r="A67" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="B67" s="5" t="s">
+      <c r="B67" s="3" t="s">
         <v>38</v>
       </c>
       <c r="C67" s="2" t="s">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="D67" s="2" t="s">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="E67" s="2" t="s">
-        <v>9</v>
+        <v>28</v>
       </c>
       <c r="F67" s="2"/>
       <c r="G67" s="2"/>
@@ -4678,17 +4675,17 @@
       <c r="A68" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="B68" s="5" t="s">
+      <c r="B68" s="3" t="s">
         <v>38</v>
       </c>
       <c r="C68" s="2" t="s">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="D68" s="2" t="s">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="E68" s="2" t="s">
-        <v>11</v>
+        <v>29</v>
       </c>
       <c r="F68" s="2"/>
       <c r="G68" s="2"/>
@@ -4731,17 +4728,17 @@
       <c r="A69" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="B69" s="5" t="s">
+      <c r="B69" s="3" t="s">
         <v>38</v>
       </c>
       <c r="C69" s="2" t="s">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="D69" s="2" t="s">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="E69" s="2" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="F69" s="2"/>
       <c r="G69" s="2"/>
@@ -4784,17 +4781,17 @@
       <c r="A70" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="B70" s="5" t="s">
+      <c r="B70" s="3" t="s">
         <v>38</v>
       </c>
       <c r="C70" s="2" t="s">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="D70" s="2" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="E70" s="2" t="s">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="F70" s="2"/>
       <c r="G70" s="2"/>
@@ -4837,17 +4834,17 @@
       <c r="A71" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="B71" s="5" t="s">
+      <c r="B71" s="3" t="s">
         <v>38</v>
       </c>
       <c r="C71" s="2" t="s">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="D71" s="2" t="s">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="E71" s="2" t="s">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="F71" s="2"/>
       <c r="G71" s="2"/>
@@ -4890,17 +4887,17 @@
       <c r="A72" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="B72" s="5" t="s">
+      <c r="B72" s="3" t="s">
         <v>38</v>
       </c>
       <c r="C72" s="2" t="s">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="D72" s="2" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="E72" s="2" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="F72" s="2"/>
       <c r="G72" s="2"/>
@@ -4943,17 +4940,17 @@
       <c r="A73" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="B73" s="5" t="s">
+      <c r="B73" s="3" t="s">
         <v>38</v>
       </c>
       <c r="C73" s="2" t="s">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="D73" s="2" t="s">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="E73" s="2" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="F73" s="2"/>
       <c r="G73" s="2"/>
@@ -4996,14 +4993,14 @@
       <c r="A74" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="B74" s="5" t="s">
+      <c r="B74" s="3" t="s">
         <v>38</v>
       </c>
       <c r="C74" s="2" t="s">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="D74" s="2" t="s">
-        <v>24</v>
+        <v>8</v>
       </c>
       <c r="E74" s="2" t="s">
         <v>11</v>
@@ -5049,17 +5046,17 @@
       <c r="A75" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="B75" s="5" t="s">
+      <c r="B75" s="3" t="s">
         <v>38</v>
       </c>
       <c r="C75" s="2" t="s">
         <v>14</v>
       </c>
       <c r="D75" s="2" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E75" s="2" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="F75" s="2"/>
       <c r="G75" s="2"/>
@@ -5102,17 +5099,17 @@
       <c r="A76" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="B76" s="5" t="s">
+      <c r="B76" s="3" t="s">
         <v>38</v>
       </c>
       <c r="C76" s="2" t="s">
         <v>14</v>
       </c>
       <c r="D76" s="2" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E76" s="2" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="F76" s="2"/>
       <c r="G76" s="2"/>
@@ -5155,17 +5152,17 @@
       <c r="A77" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="B77" s="5" t="s">
+      <c r="B77" s="3" t="s">
         <v>38</v>
       </c>
       <c r="C77" s="2" t="s">
         <v>14</v>
       </c>
       <c r="D77" s="2" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="E77" s="2" t="s">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="F77" s="2"/>
       <c r="G77" s="2"/>
@@ -5208,17 +5205,17 @@
       <c r="A78" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="B78" s="5" t="s">
+      <c r="B78" s="3" t="s">
         <v>38</v>
       </c>
       <c r="C78" s="2" t="s">
         <v>14</v>
       </c>
       <c r="D78" s="2" t="s">
-        <v>10</v>
+        <v>26</v>
       </c>
       <c r="E78" s="2" t="s">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="F78" s="2"/>
       <c r="G78" s="2"/>
@@ -5261,17 +5258,17 @@
       <c r="A79" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="B79" s="5" t="s">
+      <c r="B79" s="3" t="s">
         <v>38</v>
       </c>
       <c r="C79" s="2" t="s">
         <v>14</v>
       </c>
       <c r="D79" s="2" t="s">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="E79" s="2" t="s">
-        <v>9</v>
+        <v>28</v>
       </c>
       <c r="F79" s="2"/>
       <c r="G79" s="2"/>
@@ -5314,17 +5311,17 @@
       <c r="A80" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="B80" s="5" t="s">
+      <c r="B80" s="3" t="s">
         <v>38</v>
       </c>
       <c r="C80" s="2" t="s">
         <v>14</v>
       </c>
       <c r="D80" s="2" t="s">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="E80" s="2" t="s">
-        <v>11</v>
+        <v>29</v>
       </c>
       <c r="F80" s="2"/>
       <c r="G80" s="2"/>
@@ -5367,17 +5364,17 @@
       <c r="A81" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="B81" s="5" t="s">
+      <c r="B81" s="3" t="s">
         <v>38</v>
       </c>
       <c r="C81" s="2" t="s">
         <v>14</v>
       </c>
       <c r="D81" s="2" t="s">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="E81" s="2" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="F81" s="2"/>
       <c r="G81" s="2"/>
@@ -5417,21 +5414,11 @@
       <c r="AO81" s="2"/>
     </row>
     <row r="82" spans="1:41">
-      <c r="A82" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="B82" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="C82" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="D82" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="E82" s="2" t="s">
-        <v>22</v>
-      </c>
+      <c r="A82" s="2"/>
+      <c r="B82" s="2"/>
+      <c r="C82" s="2"/>
+      <c r="D82" s="2"/>
+      <c r="E82" s="2"/>
       <c r="F82" s="2"/>
       <c r="G82" s="2"/>
       <c r="H82" s="2"/>
@@ -5470,21 +5457,11 @@
       <c r="AO82" s="2"/>
     </row>
     <row r="83" spans="1:41">
-      <c r="A83" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="B83" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="C83" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="D83" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="E83" s="2" t="s">
-        <v>29</v>
-      </c>
+      <c r="A83" s="2"/>
+      <c r="B83" s="2"/>
+      <c r="C83" s="2"/>
+      <c r="D83" s="2"/>
+      <c r="E83" s="2"/>
       <c r="F83" s="2"/>
       <c r="G83" s="2"/>
       <c r="H83" s="2"/>
@@ -5523,21 +5500,11 @@
       <c r="AO83" s="2"/>
     </row>
     <row r="84" spans="1:41">
-      <c r="A84" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="B84" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="C84" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="D84" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="E84" s="2" t="s">
-        <v>30</v>
-      </c>
+      <c r="A84" s="2"/>
+      <c r="B84" s="2"/>
+      <c r="C84" s="2"/>
+      <c r="D84" s="2"/>
+      <c r="E84" s="2"/>
       <c r="F84" s="2"/>
       <c r="G84" s="2"/>
       <c r="H84" s="2"/>
@@ -5576,21 +5543,11 @@
       <c r="AO84" s="2"/>
     </row>
     <row r="85" spans="1:41">
-      <c r="A85" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="B85" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="C85" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="D85" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="E85" s="2" t="s">
-        <v>9</v>
-      </c>
+      <c r="A85" s="2"/>
+      <c r="B85" s="2"/>
+      <c r="C85" s="2"/>
+      <c r="D85" s="2"/>
+      <c r="E85" s="2"/>
       <c r="F85" s="2"/>
       <c r="G85" s="2"/>
       <c r="H85" s="2"/>
@@ -5629,21 +5586,11 @@
       <c r="AO85" s="2"/>
     </row>
     <row r="86" spans="1:41">
-      <c r="A86" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="B86" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="C86" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="D86" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E86" s="2" t="s">
-        <v>9</v>
-      </c>
+      <c r="A86" s="2"/>
+      <c r="B86" s="2"/>
+      <c r="C86" s="2"/>
+      <c r="D86" s="2"/>
+      <c r="E86" s="2"/>
       <c r="F86" s="2"/>
       <c r="G86" s="2"/>
       <c r="H86" s="2"/>
@@ -5682,21 +5629,11 @@
       <c r="AO86" s="2"/>
     </row>
     <row r="87" spans="1:41">
-      <c r="A87" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="B87" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="C87" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="D87" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E87" s="2" t="s">
-        <v>9</v>
-      </c>
+      <c r="A87" s="2"/>
+      <c r="B87" s="2"/>
+      <c r="C87" s="2"/>
+      <c r="D87" s="2"/>
+      <c r="E87" s="2"/>
       <c r="F87" s="2"/>
       <c r="G87" s="2"/>
       <c r="H87" s="2"/>
@@ -5735,21 +5672,11 @@
       <c r="AO87" s="2"/>
     </row>
     <row r="88" spans="1:41">
-      <c r="A88" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="B88" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="C88" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="D88" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E88" s="2" t="s">
-        <v>16</v>
-      </c>
+      <c r="A88" s="2"/>
+      <c r="B88" s="2"/>
+      <c r="C88" s="2"/>
+      <c r="D88" s="2"/>
+      <c r="E88" s="2"/>
       <c r="F88" s="2"/>
       <c r="G88" s="2"/>
       <c r="H88" s="2"/>
@@ -5788,21 +5715,11 @@
       <c r="AO88" s="2"/>
     </row>
     <row r="89" spans="1:41">
-      <c r="A89" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="B89" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="C89" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="D89" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E89" s="2" t="s">
-        <v>16</v>
-      </c>
+      <c r="A89" s="2"/>
+      <c r="B89" s="2"/>
+      <c r="C89" s="2"/>
+      <c r="D89" s="2"/>
+      <c r="E89" s="2"/>
       <c r="F89" s="2"/>
       <c r="G89" s="2"/>
       <c r="H89" s="2"/>
@@ -5841,21 +5758,11 @@
       <c r="AO89" s="2"/>
     </row>
     <row r="90" spans="1:41">
-      <c r="A90" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="B90" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="C90" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="D90" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E90" s="2" t="s">
-        <v>11</v>
-      </c>
+      <c r="A90" s="2"/>
+      <c r="B90" s="2"/>
+      <c r="C90" s="2"/>
+      <c r="D90" s="2"/>
+      <c r="E90" s="2"/>
       <c r="F90" s="2"/>
       <c r="G90" s="2"/>
       <c r="H90" s="2"/>
@@ -5894,21 +5801,11 @@
       <c r="AO90" s="2"/>
     </row>
     <row r="91" spans="1:41">
-      <c r="A91" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="B91" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="C91" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="D91" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E91" s="2" t="s">
-        <v>11</v>
-      </c>
+      <c r="A91" s="2"/>
+      <c r="B91" s="2"/>
+      <c r="C91" s="2"/>
+      <c r="D91" s="2"/>
+      <c r="E91" s="2"/>
       <c r="F91" s="2"/>
       <c r="G91" s="2"/>
       <c r="H91" s="2"/>
@@ -5947,21 +5844,11 @@
       <c r="AO91" s="2"/>
     </row>
     <row r="92" spans="1:41">
-      <c r="A92" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="B92" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="C92" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="D92" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="E92" s="2" t="s">
-        <v>9</v>
-      </c>
+      <c r="A92" s="2"/>
+      <c r="B92" s="2"/>
+      <c r="C92" s="2"/>
+      <c r="D92" s="2"/>
+      <c r="E92" s="2"/>
       <c r="F92" s="2"/>
       <c r="G92" s="2"/>
       <c r="H92" s="2"/>
@@ -6000,21 +5887,11 @@
       <c r="AO92" s="2"/>
     </row>
     <row r="93" spans="1:41">
-      <c r="A93" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="B93" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="C93" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="D93" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="E93" s="2" t="s">
-        <v>11</v>
-      </c>
+      <c r="A93" s="2"/>
+      <c r="B93" s="2"/>
+      <c r="C93" s="2"/>
+      <c r="D93" s="2"/>
+      <c r="E93" s="2"/>
       <c r="F93" s="2"/>
       <c r="G93" s="2"/>
       <c r="H93" s="2"/>
@@ -6053,21 +5930,11 @@
       <c r="AO93" s="2"/>
     </row>
     <row r="94" spans="1:41">
-      <c r="A94" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="B94" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="C94" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="D94" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="E94" s="2" t="s">
-        <v>13</v>
-      </c>
+      <c r="A94" s="2"/>
+      <c r="B94" s="2"/>
+      <c r="C94" s="2"/>
+      <c r="D94" s="2"/>
+      <c r="E94" s="2"/>
       <c r="F94" s="2"/>
       <c r="G94" s="2"/>
       <c r="H94" s="2"/>
@@ -6106,21 +5973,11 @@
       <c r="AO94" s="2"/>
     </row>
     <row r="95" spans="1:41">
-      <c r="A95" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="B95" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="C95" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="D95" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="E95" s="2" t="s">
-        <v>17</v>
-      </c>
+      <c r="A95" s="2"/>
+      <c r="B95" s="2"/>
+      <c r="C95" s="2"/>
+      <c r="D95" s="2"/>
+      <c r="E95" s="2"/>
       <c r="F95" s="2"/>
       <c r="G95" s="2"/>
       <c r="H95" s="2"/>
@@ -6159,21 +6016,11 @@
       <c r="AO95" s="2"/>
     </row>
     <row r="96" spans="1:41">
-      <c r="A96" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="B96" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="C96" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="D96" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="E96" s="2" t="s">
-        <v>22</v>
-      </c>
+      <c r="A96" s="2"/>
+      <c r="B96" s="2"/>
+      <c r="C96" s="2"/>
+      <c r="D96" s="2"/>
+      <c r="E96" s="2"/>
       <c r="F96" s="2"/>
       <c r="G96" s="2"/>
       <c r="H96" s="2"/>
@@ -6212,21 +6059,11 @@
       <c r="AO96" s="2"/>
     </row>
     <row r="97" spans="1:41">
-      <c r="A97" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="B97" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="C97" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="D97" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="E97" s="2" t="s">
-        <v>29</v>
-      </c>
+      <c r="A97" s="2"/>
+      <c r="B97" s="2"/>
+      <c r="C97" s="2"/>
+      <c r="D97" s="2"/>
+      <c r="E97" s="2"/>
       <c r="F97" s="2"/>
       <c r="G97" s="2"/>
       <c r="H97" s="2"/>
@@ -6265,21 +6102,11 @@
       <c r="AO97" s="2"/>
     </row>
     <row r="98" spans="1:41">
-      <c r="A98" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="B98" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="C98" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="D98" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="E98" s="2" t="s">
-        <v>30</v>
-      </c>
+      <c r="A98" s="2"/>
+      <c r="B98" s="2"/>
+      <c r="C98" s="2"/>
+      <c r="D98" s="2"/>
+      <c r="E98" s="2"/>
       <c r="F98" s="2"/>
       <c r="G98" s="2"/>
       <c r="H98" s="2"/>
@@ -6318,21 +6145,11 @@
       <c r="AO98" s="2"/>
     </row>
     <row r="99" spans="1:41">
-      <c r="A99" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="B99" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="C99" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="D99" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="E99" s="2" t="s">
-        <v>9</v>
-      </c>
+      <c r="A99" s="2"/>
+      <c r="B99" s="2"/>
+      <c r="C99" s="2"/>
+      <c r="D99" s="2"/>
+      <c r="E99" s="2"/>
       <c r="F99" s="2"/>
       <c r="G99" s="2"/>
       <c r="H99" s="2"/>
@@ -9940,799 +9757,25 @@
       <c r="AO182" s="2"/>
     </row>
     <row r="183" spans="1:41">
-      <c r="A183" s="2"/>
       <c r="B183" s="2"/>
-      <c r="C183" s="2"/>
-      <c r="D183" s="2"/>
-      <c r="E183" s="2"/>
-      <c r="F183" s="2"/>
-      <c r="G183" s="2"/>
-      <c r="H183" s="2"/>
-      <c r="I183" s="2"/>
-      <c r="J183" s="2"/>
-      <c r="K183" s="2"/>
-      <c r="L183" s="2"/>
-      <c r="M183" s="2"/>
-      <c r="N183" s="2"/>
-      <c r="O183" s="2"/>
-      <c r="P183" s="2"/>
-      <c r="Q183" s="2"/>
-      <c r="R183" s="2"/>
-      <c r="S183" s="2"/>
-      <c r="T183" s="2"/>
-      <c r="U183" s="2"/>
-      <c r="V183" s="2"/>
-      <c r="W183" s="2"/>
-      <c r="X183" s="2"/>
-      <c r="Y183" s="2"/>
-      <c r="Z183" s="2"/>
-      <c r="AA183" s="2"/>
-      <c r="AB183" s="2"/>
-      <c r="AC183" s="2"/>
-      <c r="AD183" s="2"/>
-      <c r="AE183" s="2"/>
-      <c r="AF183" s="2"/>
-      <c r="AG183" s="2"/>
-      <c r="AH183" s="2"/>
-      <c r="AI183" s="2"/>
-      <c r="AJ183" s="2"/>
-      <c r="AK183" s="2"/>
-      <c r="AL183" s="2"/>
-      <c r="AM183" s="2"/>
-      <c r="AN183" s="2"/>
-      <c r="AO183" s="2"/>
     </row>
     <row r="184" spans="1:41">
-      <c r="A184" s="2"/>
       <c r="B184" s="2"/>
-      <c r="C184" s="2"/>
-      <c r="D184" s="2"/>
-      <c r="E184" s="2"/>
-      <c r="F184" s="2"/>
-      <c r="G184" s="2"/>
-      <c r="H184" s="2"/>
-      <c r="I184" s="2"/>
-      <c r="J184" s="2"/>
-      <c r="K184" s="2"/>
-      <c r="L184" s="2"/>
-      <c r="M184" s="2"/>
-      <c r="N184" s="2"/>
-      <c r="O184" s="2"/>
-      <c r="P184" s="2"/>
-      <c r="Q184" s="2"/>
-      <c r="R184" s="2"/>
-      <c r="S184" s="2"/>
-      <c r="T184" s="2"/>
-      <c r="U184" s="2"/>
-      <c r="V184" s="2"/>
-      <c r="W184" s="2"/>
-      <c r="X184" s="2"/>
-      <c r="Y184" s="2"/>
-      <c r="Z184" s="2"/>
-      <c r="AA184" s="2"/>
-      <c r="AB184" s="2"/>
-      <c r="AC184" s="2"/>
-      <c r="AD184" s="2"/>
-      <c r="AE184" s="2"/>
-      <c r="AF184" s="2"/>
-      <c r="AG184" s="2"/>
-      <c r="AH184" s="2"/>
-      <c r="AI184" s="2"/>
-      <c r="AJ184" s="2"/>
-      <c r="AK184" s="2"/>
-      <c r="AL184" s="2"/>
-      <c r="AM184" s="2"/>
-      <c r="AN184" s="2"/>
-      <c r="AO184" s="2"/>
     </row>
     <row r="185" spans="1:41">
-      <c r="A185" s="2"/>
       <c r="B185" s="2"/>
-      <c r="C185" s="2"/>
-      <c r="D185" s="2"/>
-      <c r="E185" s="2"/>
-      <c r="F185" s="2"/>
-      <c r="G185" s="2"/>
-      <c r="H185" s="2"/>
-      <c r="I185" s="2"/>
-      <c r="J185" s="2"/>
-      <c r="K185" s="2"/>
-      <c r="L185" s="2"/>
-      <c r="M185" s="2"/>
-      <c r="N185" s="2"/>
-      <c r="O185" s="2"/>
-      <c r="P185" s="2"/>
-      <c r="Q185" s="2"/>
-      <c r="R185" s="2"/>
-      <c r="S185" s="2"/>
-      <c r="T185" s="2"/>
-      <c r="U185" s="2"/>
-      <c r="V185" s="2"/>
-      <c r="W185" s="2"/>
-      <c r="X185" s="2"/>
-      <c r="Y185" s="2"/>
-      <c r="Z185" s="2"/>
-      <c r="AA185" s="2"/>
-      <c r="AB185" s="2"/>
-      <c r="AC185" s="2"/>
-      <c r="AD185" s="2"/>
-      <c r="AE185" s="2"/>
-      <c r="AF185" s="2"/>
-      <c r="AG185" s="2"/>
-      <c r="AH185" s="2"/>
-      <c r="AI185" s="2"/>
-      <c r="AJ185" s="2"/>
-      <c r="AK185" s="2"/>
-      <c r="AL185" s="2"/>
-      <c r="AM185" s="2"/>
-      <c r="AN185" s="2"/>
-      <c r="AO185" s="2"/>
     </row>
     <row r="186" spans="1:41">
-      <c r="A186" s="2"/>
       <c r="B186" s="2"/>
-      <c r="C186" s="2"/>
-      <c r="D186" s="2"/>
-      <c r="E186" s="2"/>
-      <c r="F186" s="2"/>
-      <c r="G186" s="2"/>
-      <c r="H186" s="2"/>
-      <c r="I186" s="2"/>
-      <c r="J186" s="2"/>
-      <c r="K186" s="2"/>
-      <c r="L186" s="2"/>
-      <c r="M186" s="2"/>
-      <c r="N186" s="2"/>
-      <c r="O186" s="2"/>
-      <c r="P186" s="2"/>
-      <c r="Q186" s="2"/>
-      <c r="R186" s="2"/>
-      <c r="S186" s="2"/>
-      <c r="T186" s="2"/>
-      <c r="U186" s="2"/>
-      <c r="V186" s="2"/>
-      <c r="W186" s="2"/>
-      <c r="X186" s="2"/>
-      <c r="Y186" s="2"/>
-      <c r="Z186" s="2"/>
-      <c r="AA186" s="2"/>
-      <c r="AB186" s="2"/>
-      <c r="AC186" s="2"/>
-      <c r="AD186" s="2"/>
-      <c r="AE186" s="2"/>
-      <c r="AF186" s="2"/>
-      <c r="AG186" s="2"/>
-      <c r="AH186" s="2"/>
-      <c r="AI186" s="2"/>
-      <c r="AJ186" s="2"/>
-      <c r="AK186" s="2"/>
-      <c r="AL186" s="2"/>
-      <c r="AM186" s="2"/>
-      <c r="AN186" s="2"/>
-      <c r="AO186" s="2"/>
     </row>
     <row r="187" spans="1:41">
-      <c r="A187" s="2"/>
       <c r="B187" s="2"/>
-      <c r="C187" s="2"/>
-      <c r="D187" s="2"/>
-      <c r="E187" s="2"/>
-      <c r="F187" s="2"/>
-      <c r="G187" s="2"/>
-      <c r="H187" s="2"/>
-      <c r="I187" s="2"/>
-      <c r="J187" s="2"/>
-      <c r="K187" s="2"/>
-      <c r="L187" s="2"/>
-      <c r="M187" s="2"/>
-      <c r="N187" s="2"/>
-      <c r="O187" s="2"/>
-      <c r="P187" s="2"/>
-      <c r="Q187" s="2"/>
-      <c r="R187" s="2"/>
-      <c r="S187" s="2"/>
-      <c r="T187" s="2"/>
-      <c r="U187" s="2"/>
-      <c r="V187" s="2"/>
-      <c r="W187" s="2"/>
-      <c r="X187" s="2"/>
-      <c r="Y187" s="2"/>
-      <c r="Z187" s="2"/>
-      <c r="AA187" s="2"/>
-      <c r="AB187" s="2"/>
-      <c r="AC187" s="2"/>
-      <c r="AD187" s="2"/>
-      <c r="AE187" s="2"/>
-      <c r="AF187" s="2"/>
-      <c r="AG187" s="2"/>
-      <c r="AH187" s="2"/>
-      <c r="AI187" s="2"/>
-      <c r="AJ187" s="2"/>
-      <c r="AK187" s="2"/>
-      <c r="AL187" s="2"/>
-      <c r="AM187" s="2"/>
-      <c r="AN187" s="2"/>
-      <c r="AO187" s="2"/>
     </row>
     <row r="188" spans="1:41">
-      <c r="A188" s="2"/>
       <c r="B188" s="2"/>
-      <c r="C188" s="2"/>
-      <c r="D188" s="2"/>
-      <c r="E188" s="2"/>
-      <c r="F188" s="2"/>
-      <c r="G188" s="2"/>
-      <c r="H188" s="2"/>
-      <c r="I188" s="2"/>
-      <c r="J188" s="2"/>
-      <c r="K188" s="2"/>
-      <c r="L188" s="2"/>
-      <c r="M188" s="2"/>
-      <c r="N188" s="2"/>
-      <c r="O188" s="2"/>
-      <c r="P188" s="2"/>
-      <c r="Q188" s="2"/>
-      <c r="R188" s="2"/>
-      <c r="S188" s="2"/>
-      <c r="T188" s="2"/>
-      <c r="U188" s="2"/>
-      <c r="V188" s="2"/>
-      <c r="W188" s="2"/>
-      <c r="X188" s="2"/>
-      <c r="Y188" s="2"/>
-      <c r="Z188" s="2"/>
-      <c r="AA188" s="2"/>
-      <c r="AB188" s="2"/>
-      <c r="AC188" s="2"/>
-      <c r="AD188" s="2"/>
-      <c r="AE188" s="2"/>
-      <c r="AF188" s="2"/>
-      <c r="AG188" s="2"/>
-      <c r="AH188" s="2"/>
-      <c r="AI188" s="2"/>
-      <c r="AJ188" s="2"/>
-      <c r="AK188" s="2"/>
-      <c r="AL188" s="2"/>
-      <c r="AM188" s="2"/>
-      <c r="AN188" s="2"/>
-      <c r="AO188" s="2"/>
     </row>
     <row r="189" spans="1:41">
-      <c r="A189" s="2"/>
       <c r="B189" s="2"/>
-      <c r="C189" s="2"/>
-      <c r="D189" s="2"/>
-      <c r="E189" s="2"/>
-      <c r="F189" s="2"/>
-      <c r="G189" s="2"/>
-      <c r="H189" s="2"/>
-      <c r="I189" s="2"/>
-      <c r="J189" s="2"/>
-      <c r="K189" s="2"/>
-      <c r="L189" s="2"/>
-      <c r="M189" s="2"/>
-      <c r="N189" s="2"/>
-      <c r="O189" s="2"/>
-      <c r="P189" s="2"/>
-      <c r="Q189" s="2"/>
-      <c r="R189" s="2"/>
-      <c r="S189" s="2"/>
-      <c r="T189" s="2"/>
-      <c r="U189" s="2"/>
-      <c r="V189" s="2"/>
-      <c r="W189" s="2"/>
-      <c r="X189" s="2"/>
-      <c r="Y189" s="2"/>
-      <c r="Z189" s="2"/>
-      <c r="AA189" s="2"/>
-      <c r="AB189" s="2"/>
-      <c r="AC189" s="2"/>
-      <c r="AD189" s="2"/>
-      <c r="AE189" s="2"/>
-      <c r="AF189" s="2"/>
-      <c r="AG189" s="2"/>
-      <c r="AH189" s="2"/>
-      <c r="AI189" s="2"/>
-      <c r="AJ189" s="2"/>
-      <c r="AK189" s="2"/>
-      <c r="AL189" s="2"/>
-      <c r="AM189" s="2"/>
-      <c r="AN189" s="2"/>
-      <c r="AO189" s="2"/>
-    </row>
-    <row r="190" spans="1:41">
-      <c r="A190" s="2"/>
-      <c r="B190" s="2"/>
-      <c r="C190" s="2"/>
-      <c r="D190" s="2"/>
-      <c r="E190" s="2"/>
-      <c r="F190" s="2"/>
-      <c r="G190" s="2"/>
-      <c r="H190" s="2"/>
-      <c r="I190" s="2"/>
-      <c r="J190" s="2"/>
-      <c r="K190" s="2"/>
-      <c r="L190" s="2"/>
-      <c r="M190" s="2"/>
-      <c r="N190" s="2"/>
-      <c r="O190" s="2"/>
-      <c r="P190" s="2"/>
-      <c r="Q190" s="2"/>
-      <c r="R190" s="2"/>
-      <c r="S190" s="2"/>
-      <c r="T190" s="2"/>
-      <c r="U190" s="2"/>
-      <c r="V190" s="2"/>
-      <c r="W190" s="2"/>
-      <c r="X190" s="2"/>
-      <c r="Y190" s="2"/>
-      <c r="Z190" s="2"/>
-      <c r="AA190" s="2"/>
-      <c r="AB190" s="2"/>
-      <c r="AC190" s="2"/>
-      <c r="AD190" s="2"/>
-      <c r="AE190" s="2"/>
-      <c r="AF190" s="2"/>
-      <c r="AG190" s="2"/>
-      <c r="AH190" s="2"/>
-      <c r="AI190" s="2"/>
-      <c r="AJ190" s="2"/>
-      <c r="AK190" s="2"/>
-      <c r="AL190" s="2"/>
-      <c r="AM190" s="2"/>
-      <c r="AN190" s="2"/>
-      <c r="AO190" s="2"/>
-    </row>
-    <row r="191" spans="1:41">
-      <c r="A191" s="2"/>
-      <c r="B191" s="2"/>
-      <c r="C191" s="2"/>
-      <c r="D191" s="2"/>
-      <c r="E191" s="2"/>
-      <c r="F191" s="2"/>
-      <c r="G191" s="2"/>
-      <c r="H191" s="2"/>
-      <c r="I191" s="2"/>
-      <c r="J191" s="2"/>
-      <c r="K191" s="2"/>
-      <c r="L191" s="2"/>
-      <c r="M191" s="2"/>
-      <c r="N191" s="2"/>
-      <c r="O191" s="2"/>
-      <c r="P191" s="2"/>
-      <c r="Q191" s="2"/>
-      <c r="R191" s="2"/>
-      <c r="S191" s="2"/>
-      <c r="T191" s="2"/>
-      <c r="U191" s="2"/>
-      <c r="V191" s="2"/>
-      <c r="W191" s="2"/>
-      <c r="X191" s="2"/>
-      <c r="Y191" s="2"/>
-      <c r="Z191" s="2"/>
-      <c r="AA191" s="2"/>
-      <c r="AB191" s="2"/>
-      <c r="AC191" s="2"/>
-      <c r="AD191" s="2"/>
-      <c r="AE191" s="2"/>
-      <c r="AF191" s="2"/>
-      <c r="AG191" s="2"/>
-      <c r="AH191" s="2"/>
-      <c r="AI191" s="2"/>
-      <c r="AJ191" s="2"/>
-      <c r="AK191" s="2"/>
-      <c r="AL191" s="2"/>
-      <c r="AM191" s="2"/>
-      <c r="AN191" s="2"/>
-      <c r="AO191" s="2"/>
-    </row>
-    <row r="192" spans="1:41">
-      <c r="A192" s="2"/>
-      <c r="B192" s="2"/>
-      <c r="C192" s="2"/>
-      <c r="D192" s="2"/>
-      <c r="E192" s="2"/>
-      <c r="F192" s="2"/>
-      <c r="G192" s="2"/>
-      <c r="H192" s="2"/>
-      <c r="I192" s="2"/>
-      <c r="J192" s="2"/>
-      <c r="K192" s="2"/>
-      <c r="L192" s="2"/>
-      <c r="M192" s="2"/>
-      <c r="N192" s="2"/>
-      <c r="O192" s="2"/>
-      <c r="P192" s="2"/>
-      <c r="Q192" s="2"/>
-      <c r="R192" s="2"/>
-      <c r="S192" s="2"/>
-      <c r="T192" s="2"/>
-      <c r="U192" s="2"/>
-      <c r="V192" s="2"/>
-      <c r="W192" s="2"/>
-      <c r="X192" s="2"/>
-      <c r="Y192" s="2"/>
-      <c r="Z192" s="2"/>
-      <c r="AA192" s="2"/>
-      <c r="AB192" s="2"/>
-      <c r="AC192" s="2"/>
-      <c r="AD192" s="2"/>
-      <c r="AE192" s="2"/>
-      <c r="AF192" s="2"/>
-      <c r="AG192" s="2"/>
-      <c r="AH192" s="2"/>
-      <c r="AI192" s="2"/>
-      <c r="AJ192" s="2"/>
-      <c r="AK192" s="2"/>
-      <c r="AL192" s="2"/>
-      <c r="AM192" s="2"/>
-      <c r="AN192" s="2"/>
-      <c r="AO192" s="2"/>
-    </row>
-    <row r="193" spans="1:41">
-      <c r="A193" s="2"/>
-      <c r="B193" s="2"/>
-      <c r="C193" s="2"/>
-      <c r="D193" s="2"/>
-      <c r="E193" s="2"/>
-      <c r="F193" s="2"/>
-      <c r="G193" s="2"/>
-      <c r="H193" s="2"/>
-      <c r="I193" s="2"/>
-      <c r="J193" s="2"/>
-      <c r="K193" s="2"/>
-      <c r="L193" s="2"/>
-      <c r="M193" s="2"/>
-      <c r="N193" s="2"/>
-      <c r="O193" s="2"/>
-      <c r="P193" s="2"/>
-      <c r="Q193" s="2"/>
-      <c r="R193" s="2"/>
-      <c r="S193" s="2"/>
-      <c r="T193" s="2"/>
-      <c r="U193" s="2"/>
-      <c r="V193" s="2"/>
-      <c r="W193" s="2"/>
-      <c r="X193" s="2"/>
-      <c r="Y193" s="2"/>
-      <c r="Z193" s="2"/>
-      <c r="AA193" s="2"/>
-      <c r="AB193" s="2"/>
-      <c r="AC193" s="2"/>
-      <c r="AD193" s="2"/>
-      <c r="AE193" s="2"/>
-      <c r="AF193" s="2"/>
-      <c r="AG193" s="2"/>
-      <c r="AH193" s="2"/>
-      <c r="AI193" s="2"/>
-      <c r="AJ193" s="2"/>
-      <c r="AK193" s="2"/>
-      <c r="AL193" s="2"/>
-      <c r="AM193" s="2"/>
-      <c r="AN193" s="2"/>
-      <c r="AO193" s="2"/>
-    </row>
-    <row r="194" spans="1:41">
-      <c r="A194" s="2"/>
-      <c r="B194" s="2"/>
-      <c r="C194" s="2"/>
-      <c r="D194" s="2"/>
-      <c r="E194" s="2"/>
-      <c r="F194" s="2"/>
-      <c r="G194" s="2"/>
-      <c r="H194" s="2"/>
-      <c r="I194" s="2"/>
-      <c r="J194" s="2"/>
-      <c r="K194" s="2"/>
-      <c r="L194" s="2"/>
-      <c r="M194" s="2"/>
-      <c r="N194" s="2"/>
-      <c r="O194" s="2"/>
-      <c r="P194" s="2"/>
-      <c r="Q194" s="2"/>
-      <c r="R194" s="2"/>
-      <c r="S194" s="2"/>
-      <c r="T194" s="2"/>
-      <c r="U194" s="2"/>
-      <c r="V194" s="2"/>
-      <c r="W194" s="2"/>
-      <c r="X194" s="2"/>
-      <c r="Y194" s="2"/>
-      <c r="Z194" s="2"/>
-      <c r="AA194" s="2"/>
-      <c r="AB194" s="2"/>
-      <c r="AC194" s="2"/>
-      <c r="AD194" s="2"/>
-      <c r="AE194" s="2"/>
-      <c r="AF194" s="2"/>
-      <c r="AG194" s="2"/>
-      <c r="AH194" s="2"/>
-      <c r="AI194" s="2"/>
-      <c r="AJ194" s="2"/>
-      <c r="AK194" s="2"/>
-      <c r="AL194" s="2"/>
-      <c r="AM194" s="2"/>
-      <c r="AN194" s="2"/>
-      <c r="AO194" s="2"/>
-    </row>
-    <row r="195" spans="1:41">
-      <c r="A195" s="2"/>
-      <c r="B195" s="2"/>
-      <c r="C195" s="2"/>
-      <c r="D195" s="2"/>
-      <c r="E195" s="2"/>
-      <c r="F195" s="2"/>
-      <c r="G195" s="2"/>
-      <c r="H195" s="2"/>
-      <c r="I195" s="2"/>
-      <c r="J195" s="2"/>
-      <c r="K195" s="2"/>
-      <c r="L195" s="2"/>
-      <c r="M195" s="2"/>
-      <c r="N195" s="2"/>
-      <c r="O195" s="2"/>
-      <c r="P195" s="2"/>
-      <c r="Q195" s="2"/>
-      <c r="R195" s="2"/>
-      <c r="S195" s="2"/>
-      <c r="T195" s="2"/>
-      <c r="U195" s="2"/>
-      <c r="V195" s="2"/>
-      <c r="W195" s="2"/>
-      <c r="X195" s="2"/>
-      <c r="Y195" s="2"/>
-      <c r="Z195" s="2"/>
-      <c r="AA195" s="2"/>
-      <c r="AB195" s="2"/>
-      <c r="AC195" s="2"/>
-      <c r="AD195" s="2"/>
-      <c r="AE195" s="2"/>
-      <c r="AF195" s="2"/>
-      <c r="AG195" s="2"/>
-      <c r="AH195" s="2"/>
-      <c r="AI195" s="2"/>
-      <c r="AJ195" s="2"/>
-      <c r="AK195" s="2"/>
-      <c r="AL195" s="2"/>
-      <c r="AM195" s="2"/>
-      <c r="AN195" s="2"/>
-      <c r="AO195" s="2"/>
-    </row>
-    <row r="196" spans="1:41">
-      <c r="A196" s="2"/>
-      <c r="B196" s="2"/>
-      <c r="C196" s="2"/>
-      <c r="D196" s="2"/>
-      <c r="E196" s="2"/>
-      <c r="F196" s="2"/>
-      <c r="G196" s="2"/>
-      <c r="H196" s="2"/>
-      <c r="I196" s="2"/>
-      <c r="J196" s="2"/>
-      <c r="K196" s="2"/>
-      <c r="L196" s="2"/>
-      <c r="M196" s="2"/>
-      <c r="N196" s="2"/>
-      <c r="O196" s="2"/>
-      <c r="P196" s="2"/>
-      <c r="Q196" s="2"/>
-      <c r="R196" s="2"/>
-      <c r="S196" s="2"/>
-      <c r="T196" s="2"/>
-      <c r="U196" s="2"/>
-      <c r="V196" s="2"/>
-      <c r="W196" s="2"/>
-      <c r="X196" s="2"/>
-      <c r="Y196" s="2"/>
-      <c r="Z196" s="2"/>
-      <c r="AA196" s="2"/>
-      <c r="AB196" s="2"/>
-      <c r="AC196" s="2"/>
-      <c r="AD196" s="2"/>
-      <c r="AE196" s="2"/>
-      <c r="AF196" s="2"/>
-      <c r="AG196" s="2"/>
-      <c r="AH196" s="2"/>
-      <c r="AI196" s="2"/>
-      <c r="AJ196" s="2"/>
-      <c r="AK196" s="2"/>
-      <c r="AL196" s="2"/>
-      <c r="AM196" s="2"/>
-      <c r="AN196" s="2"/>
-      <c r="AO196" s="2"/>
-    </row>
-    <row r="197" spans="1:41">
-      <c r="A197" s="2"/>
-      <c r="B197" s="2"/>
-      <c r="C197" s="2"/>
-      <c r="D197" s="2"/>
-      <c r="E197" s="2"/>
-      <c r="F197" s="2"/>
-      <c r="G197" s="2"/>
-      <c r="H197" s="2"/>
-      <c r="I197" s="2"/>
-      <c r="J197" s="2"/>
-      <c r="K197" s="2"/>
-      <c r="L197" s="2"/>
-      <c r="M197" s="2"/>
-      <c r="N197" s="2"/>
-      <c r="O197" s="2"/>
-      <c r="P197" s="2"/>
-      <c r="Q197" s="2"/>
-      <c r="R197" s="2"/>
-      <c r="S197" s="2"/>
-      <c r="T197" s="2"/>
-      <c r="U197" s="2"/>
-      <c r="V197" s="2"/>
-      <c r="W197" s="2"/>
-      <c r="X197" s="2"/>
-      <c r="Y197" s="2"/>
-      <c r="Z197" s="2"/>
-      <c r="AA197" s="2"/>
-      <c r="AB197" s="2"/>
-      <c r="AC197" s="2"/>
-      <c r="AD197" s="2"/>
-      <c r="AE197" s="2"/>
-      <c r="AF197" s="2"/>
-      <c r="AG197" s="2"/>
-      <c r="AH197" s="2"/>
-      <c r="AI197" s="2"/>
-      <c r="AJ197" s="2"/>
-      <c r="AK197" s="2"/>
-      <c r="AL197" s="2"/>
-      <c r="AM197" s="2"/>
-      <c r="AN197" s="2"/>
-      <c r="AO197" s="2"/>
-    </row>
-    <row r="198" spans="1:41">
-      <c r="A198" s="2"/>
-      <c r="B198" s="2"/>
-      <c r="C198" s="2"/>
-      <c r="D198" s="2"/>
-      <c r="E198" s="2"/>
-      <c r="F198" s="2"/>
-      <c r="G198" s="2"/>
-      <c r="H198" s="2"/>
-      <c r="I198" s="2"/>
-      <c r="J198" s="2"/>
-      <c r="K198" s="2"/>
-      <c r="L198" s="2"/>
-      <c r="M198" s="2"/>
-      <c r="N198" s="2"/>
-      <c r="O198" s="2"/>
-      <c r="P198" s="2"/>
-      <c r="Q198" s="2"/>
-      <c r="R198" s="2"/>
-      <c r="S198" s="2"/>
-      <c r="T198" s="2"/>
-      <c r="U198" s="2"/>
-      <c r="V198" s="2"/>
-      <c r="W198" s="2"/>
-      <c r="X198" s="2"/>
-      <c r="Y198" s="2"/>
-      <c r="Z198" s="2"/>
-      <c r="AA198" s="2"/>
-      <c r="AB198" s="2"/>
-      <c r="AC198" s="2"/>
-      <c r="AD198" s="2"/>
-      <c r="AE198" s="2"/>
-      <c r="AF198" s="2"/>
-      <c r="AG198" s="2"/>
-      <c r="AH198" s="2"/>
-      <c r="AI198" s="2"/>
-      <c r="AJ198" s="2"/>
-      <c r="AK198" s="2"/>
-      <c r="AL198" s="2"/>
-      <c r="AM198" s="2"/>
-      <c r="AN198" s="2"/>
-      <c r="AO198" s="2"/>
-    </row>
-    <row r="199" spans="1:41">
-      <c r="A199" s="2"/>
-      <c r="B199" s="2"/>
-      <c r="C199" s="2"/>
-      <c r="D199" s="2"/>
-      <c r="E199" s="2"/>
-      <c r="F199" s="2"/>
-      <c r="G199" s="2"/>
-      <c r="H199" s="2"/>
-      <c r="I199" s="2"/>
-      <c r="J199" s="2"/>
-      <c r="K199" s="2"/>
-      <c r="L199" s="2"/>
-      <c r="M199" s="2"/>
-      <c r="N199" s="2"/>
-      <c r="O199" s="2"/>
-      <c r="P199" s="2"/>
-      <c r="Q199" s="2"/>
-      <c r="R199" s="2"/>
-      <c r="S199" s="2"/>
-      <c r="T199" s="2"/>
-      <c r="U199" s="2"/>
-      <c r="V199" s="2"/>
-      <c r="W199" s="2"/>
-      <c r="X199" s="2"/>
-      <c r="Y199" s="2"/>
-      <c r="Z199" s="2"/>
-      <c r="AA199" s="2"/>
-      <c r="AB199" s="2"/>
-      <c r="AC199" s="2"/>
-      <c r="AD199" s="2"/>
-      <c r="AE199" s="2"/>
-      <c r="AF199" s="2"/>
-      <c r="AG199" s="2"/>
-      <c r="AH199" s="2"/>
-      <c r="AI199" s="2"/>
-      <c r="AJ199" s="2"/>
-      <c r="AK199" s="2"/>
-      <c r="AL199" s="2"/>
-      <c r="AM199" s="2"/>
-      <c r="AN199" s="2"/>
-      <c r="AO199" s="2"/>
-    </row>
-    <row r="200" spans="1:41">
-      <c r="A200" s="2"/>
-      <c r="B200" s="2"/>
-      <c r="C200" s="2"/>
-      <c r="D200" s="2"/>
-      <c r="E200" s="2"/>
-      <c r="F200" s="2"/>
-      <c r="G200" s="2"/>
-      <c r="H200" s="2"/>
-      <c r="I200" s="2"/>
-      <c r="J200" s="2"/>
-      <c r="K200" s="2"/>
-      <c r="L200" s="2"/>
-      <c r="M200" s="2"/>
-      <c r="N200" s="2"/>
-      <c r="O200" s="2"/>
-      <c r="P200" s="2"/>
-      <c r="Q200" s="2"/>
-      <c r="R200" s="2"/>
-      <c r="S200" s="2"/>
-      <c r="T200" s="2"/>
-      <c r="U200" s="2"/>
-      <c r="V200" s="2"/>
-      <c r="W200" s="2"/>
-      <c r="X200" s="2"/>
-      <c r="Y200" s="2"/>
-      <c r="Z200" s="2"/>
-      <c r="AA200" s="2"/>
-      <c r="AB200" s="2"/>
-      <c r="AC200" s="2"/>
-      <c r="AD200" s="2"/>
-      <c r="AE200" s="2"/>
-      <c r="AF200" s="2"/>
-      <c r="AG200" s="2"/>
-      <c r="AH200" s="2"/>
-      <c r="AI200" s="2"/>
-      <c r="AJ200" s="2"/>
-      <c r="AK200" s="2"/>
-      <c r="AL200" s="2"/>
-      <c r="AM200" s="2"/>
-      <c r="AN200" s="2"/>
-      <c r="AO200" s="2"/>
-    </row>
-    <row r="201" spans="1:41">
-      <c r="B201" s="2"/>
-    </row>
-    <row r="202" spans="1:41">
-      <c r="B202" s="2"/>
-    </row>
-    <row r="203" spans="1:41">
-      <c r="B203" s="2"/>
-    </row>
-    <row r="204" spans="1:41">
-      <c r="B204" s="2"/>
-    </row>
-    <row r="205" spans="1:41">
-      <c r="B205" s="2"/>
-    </row>
-    <row r="206" spans="1:41">
-      <c r="B206" s="2"/>
-    </row>
-    <row r="207" spans="1:41">
-      <c r="B207" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
